--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/50.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/50.xlsx
@@ -426,13 +426,13 @@
         <v>-8.584667245540663</v>
       </c>
       <c r="E2">
-        <v>-14.15566313218655</v>
+        <v>-12.03788603470744</v>
       </c>
       <c r="F2">
-        <v>0.04557745562192385</v>
+        <v>0.9674211496229369</v>
       </c>
       <c r="G2">
-        <v>-12.21704003135017</v>
+        <v>-11.73676106925113</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.225556156722572</v>
       </c>
       <c r="E3">
-        <v>-13.62009862519541</v>
+        <v>-11.24461965736181</v>
       </c>
       <c r="F3">
-        <v>0.5256461867707382</v>
+        <v>0.5998024650367527</v>
       </c>
       <c r="G3">
-        <v>-12.80649835961818</v>
+        <v>-12.39790096370677</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.792403803314997</v>
       </c>
       <c r="E4">
-        <v>-14.77570179331677</v>
+        <v>-13.35409153351084</v>
       </c>
       <c r="F4">
-        <v>0.8174833362466152</v>
+        <v>1.408932691641045</v>
       </c>
       <c r="G4">
-        <v>-13.02992001682233</v>
+        <v>-12.52187535788727</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.318484207972406</v>
       </c>
       <c r="E5">
-        <v>-15.42495816874449</v>
+        <v>-13.31058648371915</v>
       </c>
       <c r="F5">
-        <v>0.800110815075104</v>
+        <v>0.7770258722938873</v>
       </c>
       <c r="G5">
-        <v>-12.6758958978876</v>
+        <v>-12.23322629730291</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.809062171047224</v>
       </c>
       <c r="E6">
-        <v>-16.76027382786025</v>
+        <v>-13.74734874481094</v>
       </c>
       <c r="F6">
-        <v>0.7643336269481933</v>
+        <v>1.48760440061972</v>
       </c>
       <c r="G6">
-        <v>-12.79580813977751</v>
+        <v>-10.88922154044656</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.278366217065209</v>
       </c>
       <c r="E7">
-        <v>-16.14443306213514</v>
+        <v>-14.70195106562785</v>
       </c>
       <c r="F7">
-        <v>0.7740271822957531</v>
+        <v>1.681294923477106</v>
       </c>
       <c r="G7">
-        <v>-12.60319715301654</v>
+        <v>-10.71390587252543</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.740545675445472</v>
       </c>
       <c r="E8">
-        <v>-18.13731031800869</v>
+        <v>-14.15910024395837</v>
       </c>
       <c r="F8">
-        <v>0.8685306490767319</v>
+        <v>1.451562134923914</v>
       </c>
       <c r="G8">
-        <v>-11.80728436422828</v>
+        <v>-11.0335165397447</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.208840549732156</v>
       </c>
       <c r="E9">
-        <v>-18.28860210613094</v>
+        <v>-16.32315834579586</v>
       </c>
       <c r="F9">
-        <v>0.7817343126113997</v>
+        <v>1.409875373745431</v>
       </c>
       <c r="G9">
-        <v>-11.42288925853933</v>
+        <v>-10.13535432472102</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.691501713931481</v>
       </c>
       <c r="E10">
-        <v>-18.81467493160201</v>
+        <v>-17.4974550546209</v>
       </c>
       <c r="F10">
-        <v>0.847884419929357</v>
+        <v>2.02292192406565</v>
       </c>
       <c r="G10">
-        <v>-10.27369718811033</v>
+        <v>-10.35057292802656</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.197207015271885</v>
       </c>
       <c r="E11">
-        <v>-19.00337644350164</v>
+        <v>-16.29343797088352</v>
       </c>
       <c r="F11">
-        <v>0.2737305475379777</v>
+        <v>2.422201639154234</v>
       </c>
       <c r="G11">
-        <v>-10.10472084024204</v>
+        <v>-9.875977041668476</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.734252058140527</v>
       </c>
       <c r="E12">
-        <v>-20.51387159113012</v>
+        <v>-20.13021927320029</v>
       </c>
       <c r="F12">
-        <v>0.2839070410813696</v>
+        <v>1.911610882681869</v>
       </c>
       <c r="G12">
-        <v>-9.232483556759533</v>
+        <v>-9.603166437551563</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.307804830463927</v>
       </c>
       <c r="E13">
-        <v>-21.90726945786827</v>
+        <v>-19.77730623683452</v>
       </c>
       <c r="F13">
-        <v>1.301372497857141</v>
+        <v>1.835038256701889</v>
       </c>
       <c r="G13">
-        <v>-8.829821890649157</v>
+        <v>-7.158252785513437</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.929582245875463</v>
       </c>
       <c r="E14">
-        <v>-22.59585110157859</v>
+        <v>-19.07622147638902</v>
       </c>
       <c r="F14">
-        <v>0.9324955231861041</v>
+        <v>1.312008735309086</v>
       </c>
       <c r="G14">
-        <v>-7.969101694840298</v>
+        <v>-6.615984985713366</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.604606190801966</v>
       </c>
       <c r="E15">
-        <v>-22.45915005670905</v>
+        <v>-23.19115070920491</v>
       </c>
       <c r="F15">
-        <v>1.156144781533137</v>
+        <v>1.963228112285112</v>
       </c>
       <c r="G15">
-        <v>-7.538454490049416</v>
+        <v>-6.02653321988848</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.33517677098241</v>
       </c>
       <c r="E16">
-        <v>-24.34453039658851</v>
+        <v>-21.49056380815645</v>
       </c>
       <c r="F16">
-        <v>0.7018979190643889</v>
+        <v>1.805578198388727</v>
       </c>
       <c r="G16">
-        <v>-6.66566268012336</v>
+        <v>-5.74910265581587</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.120655535417632</v>
       </c>
       <c r="E17">
-        <v>-23.09533725615062</v>
+        <v>-22.59552052297603</v>
       </c>
       <c r="F17">
-        <v>0.4578865615891414</v>
+        <v>1.924776954181965</v>
       </c>
       <c r="G17">
-        <v>-5.737329632860582</v>
+        <v>-5.59522648956415</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.95990478002351</v>
       </c>
       <c r="E18">
-        <v>-24.93292860982715</v>
+        <v>-23.48817784784202</v>
       </c>
       <c r="F18">
-        <v>1.121537248178979</v>
+        <v>2.510237213254154</v>
       </c>
       <c r="G18">
-        <v>-5.428661839542058</v>
+        <v>-5.668981787777349</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.848791189103249</v>
       </c>
       <c r="E19">
-        <v>-25.47537639730995</v>
+        <v>-22.15347353271729</v>
       </c>
       <c r="F19">
-        <v>0.6745062941560177</v>
+        <v>1.574261571361382</v>
       </c>
       <c r="G19">
-        <v>-4.858280533420665</v>
+        <v>-5.392197624351949</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.787297014792729</v>
       </c>
       <c r="E20">
-        <v>-26.45870282875751</v>
+        <v>-23.22444405010931</v>
       </c>
       <c r="F20">
-        <v>0.8644318871676799</v>
+        <v>2.549407394262932</v>
       </c>
       <c r="G20">
-        <v>-3.843283862329833</v>
+        <v>-3.810848987214722</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.772013529499411</v>
       </c>
       <c r="E21">
-        <v>-25.84594595383162</v>
+        <v>-26.25879334368891</v>
       </c>
       <c r="F21">
-        <v>1.116648223767657</v>
+        <v>2.975254508694102</v>
       </c>
       <c r="G21">
-        <v>-4.341629230335178</v>
+        <v>-2.62644284700976</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.798793378838573</v>
       </c>
       <c r="E22">
-        <v>-27.34170544703915</v>
+        <v>-27.60471016045663</v>
       </c>
       <c r="F22">
-        <v>0.8775118084578841</v>
+        <v>2.02738682436674</v>
       </c>
       <c r="G22">
-        <v>-3.259439704150038</v>
+        <v>-2.99079953263518</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.86258783667635</v>
       </c>
       <c r="E23">
-        <v>-27.67122438668129</v>
+        <v>-26.4509002680423</v>
       </c>
       <c r="F23">
-        <v>0.4793073142581338</v>
+        <v>2.780417525351241</v>
       </c>
       <c r="G23">
-        <v>-2.638015715449922</v>
+        <v>-3.687609586663538</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.959515955448438</v>
       </c>
       <c r="E24">
-        <v>-29.19059987183882</v>
+        <v>-26.41770202509207</v>
       </c>
       <c r="F24">
-        <v>1.171081902540418</v>
+        <v>2.417079015135322</v>
       </c>
       <c r="G24">
-        <v>-2.947241316433551</v>
+        <v>-2.795242008913834</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.08386521210674</v>
       </c>
       <c r="E25">
-        <v>-28.89960013210592</v>
+        <v>-25.68631271658723</v>
       </c>
       <c r="F25">
-        <v>1.251173433247491</v>
+        <v>3.026104670082352</v>
       </c>
       <c r="G25">
-        <v>-2.382428243298535</v>
+        <v>-2.446146284761392</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.231039681096244</v>
       </c>
       <c r="E26">
-        <v>-29.32097011004564</v>
+        <v>-27.20601425187331</v>
       </c>
       <c r="F26">
-        <v>0.6163283947226028</v>
+        <v>3.28514178387698</v>
       </c>
       <c r="G26">
-        <v>-2.11560258730605</v>
+        <v>-1.479173572414594</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.394313359852417</v>
       </c>
       <c r="E27">
-        <v>-28.57334622222331</v>
+        <v>-25.46213061083751</v>
       </c>
       <c r="F27">
-        <v>0.9703005547150679</v>
+        <v>3.29002418134908</v>
       </c>
       <c r="G27">
-        <v>-2.563899482865184</v>
+        <v>-3.548032983967879</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.565995085717753</v>
       </c>
       <c r="E28">
-        <v>-29.58603980761062</v>
+        <v>-28.66474441312012</v>
       </c>
       <c r="F28">
-        <v>0.9426662181576765</v>
+        <v>3.030912514488201</v>
       </c>
       <c r="G28">
-        <v>-1.971671803601008</v>
+        <v>-2.171668820092282</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.738098041093107</v>
       </c>
       <c r="E29">
-        <v>-28.26864784861721</v>
+        <v>-27.78569968112119</v>
       </c>
       <c r="F29">
-        <v>0.8496852906630431</v>
+        <v>2.993409008693856</v>
       </c>
       <c r="G29">
-        <v>-2.10810171482116</v>
+        <v>-1.642739185931354</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.905316236441485</v>
       </c>
       <c r="E30">
-        <v>-27.84600989795534</v>
+        <v>-27.73438754214028</v>
       </c>
       <c r="F30">
-        <v>1.326337834642712</v>
+        <v>2.669164469685656</v>
       </c>
       <c r="G30">
-        <v>-2.691794936809221</v>
+        <v>-2.905750269814373</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.062433864018133</v>
       </c>
       <c r="E31">
-        <v>-28.178191580314</v>
+        <v>-27.48681586814094</v>
       </c>
       <c r="F31">
-        <v>1.127693674716585</v>
+        <v>2.042318975169603</v>
       </c>
       <c r="G31">
-        <v>-1.946291554838703</v>
+        <v>-2.147017002516174</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.206640898941847</v>
       </c>
       <c r="E32">
-        <v>-28.81177943567517</v>
+        <v>-25.43238759355513</v>
       </c>
       <c r="F32">
-        <v>0.7462039779705233</v>
+        <v>2.966994028953385</v>
       </c>
       <c r="G32">
-        <v>-2.46353019658333</v>
+        <v>-3.286791967069569</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.335484992828702</v>
       </c>
       <c r="E33">
-        <v>-28.21812819258764</v>
+        <v>-24.73558224104688</v>
       </c>
       <c r="F33">
-        <v>0.8131078996250282</v>
+        <v>3.192064765763622</v>
       </c>
       <c r="G33">
-        <v>-3.03098137185214</v>
+        <v>-2.34068454261928</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.446717494361405</v>
       </c>
       <c r="E34">
-        <v>-27.61589549125557</v>
+        <v>-24.87105154098634</v>
       </c>
       <c r="F34">
-        <v>0.8063401379441562</v>
+        <v>2.021409325188138</v>
       </c>
       <c r="G34">
-        <v>-3.720326646832761</v>
+        <v>-3.299027642264738</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.538903495580724</v>
       </c>
       <c r="E35">
-        <v>-27.06213557570161</v>
+        <v>-25.36903877066183</v>
       </c>
       <c r="F35">
-        <v>1.011099306037749</v>
+        <v>3.230343623446987</v>
       </c>
       <c r="G35">
-        <v>-3.768580291085955</v>
+        <v>-5.686067108437377</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.61307823654203</v>
       </c>
       <c r="E36">
-        <v>-25.61226763808782</v>
+        <v>-25.39846026628967</v>
       </c>
       <c r="F36">
-        <v>0.5769478083935143</v>
+        <v>2.890905169536639</v>
       </c>
       <c r="G36">
-        <v>-3.341946020262275</v>
+        <v>-4.047136314153455</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.670261812618496</v>
       </c>
       <c r="E37">
-        <v>-25.95352891083185</v>
+        <v>-25.37413330392046</v>
       </c>
       <c r="F37">
-        <v>1.262749039334211</v>
+        <v>3.554677626134689</v>
       </c>
       <c r="G37">
-        <v>-3.644454960713721</v>
+        <v>-3.960003475642401</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.713765384175343</v>
       </c>
       <c r="E38">
-        <v>-25.55645419594328</v>
+        <v>-23.58015568341181</v>
       </c>
       <c r="F38">
-        <v>1.300477861062117</v>
+        <v>2.560500890521223</v>
       </c>
       <c r="G38">
-        <v>-5.213499017003031</v>
+        <v>-5.60066347368815</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.74701160297885</v>
       </c>
       <c r="E39">
-        <v>-25.35004182219966</v>
+        <v>-24.25738444278491</v>
       </c>
       <c r="F39">
-        <v>1.5707161588774</v>
+        <v>3.884813514111598</v>
       </c>
       <c r="G39">
-        <v>-4.924052619579734</v>
+        <v>-7.047990616229858</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.773178407197615</v>
       </c>
       <c r="E40">
-        <v>-22.62280910734625</v>
+        <v>-22.95353714954844</v>
       </c>
       <c r="F40">
-        <v>1.394073437169628</v>
+        <v>3.538670254442991</v>
       </c>
       <c r="G40">
-        <v>-5.066608571451368</v>
+        <v>-5.568625626381732</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.796406825255034</v>
       </c>
       <c r="E41">
-        <v>-24.46618332233057</v>
+        <v>-21.57397377090373</v>
       </c>
       <c r="F41">
-        <v>2.251009574956883</v>
+        <v>3.683836671579188</v>
       </c>
       <c r="G41">
-        <v>-6.060031210788851</v>
+        <v>-5.659584369231099</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.822657491184448</v>
       </c>
       <c r="E42">
-        <v>-23.12784264257768</v>
+        <v>-21.14360571511077</v>
       </c>
       <c r="F42">
-        <v>1.32551443744433</v>
+        <v>3.072506498517569</v>
       </c>
       <c r="G42">
-        <v>-6.430632061041893</v>
+        <v>-6.233575019067882</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.857035258233872</v>
       </c>
       <c r="E43">
-        <v>-21.98409049093439</v>
+        <v>-20.64707665406575</v>
       </c>
       <c r="F43">
-        <v>1.713303039921279</v>
+        <v>3.262118140283571</v>
       </c>
       <c r="G43">
-        <v>-6.743919814316116</v>
+        <v>-6.40955677496558</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.905536198884282</v>
       </c>
       <c r="E44">
-        <v>-21.72513876175377</v>
+        <v>-23.37426861265308</v>
       </c>
       <c r="F44">
-        <v>2.200906600965958</v>
+        <v>3.064090285705126</v>
       </c>
       <c r="G44">
-        <v>-6.500846921192451</v>
+        <v>-7.134040651626295</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.971658605326217</v>
       </c>
       <c r="E45">
-        <v>-20.87490418139164</v>
+        <v>-20.92326828379356</v>
       </c>
       <c r="F45">
-        <v>2.425761962251467</v>
+        <v>2.879813330013154</v>
       </c>
       <c r="G45">
-        <v>-7.278004247546932</v>
+        <v>-7.7971328729098</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.055739210539574</v>
       </c>
       <c r="E46">
-        <v>-21.10599673847707</v>
+        <v>-16.37924802485487</v>
       </c>
       <c r="F46">
-        <v>2.638297843522541</v>
+        <v>4.298763615903762</v>
       </c>
       <c r="G46">
-        <v>-6.762603089875594</v>
+        <v>-7.559782430185806</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.157089728526151</v>
       </c>
       <c r="E47">
-        <v>-20.33011064437287</v>
+        <v>-17.68934008374791</v>
       </c>
       <c r="F47">
-        <v>2.176244446649811</v>
+        <v>3.180702878466824</v>
       </c>
       <c r="G47">
-        <v>-6.537855819161428</v>
+        <v>-7.350712836082668</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.274315630640666</v>
       </c>
       <c r="E48">
-        <v>-18.11957681379465</v>
+        <v>-17.66832796435232</v>
       </c>
       <c r="F48">
-        <v>2.768005268187693</v>
+        <v>3.570635295782218</v>
       </c>
       <c r="G48">
-        <v>-7.998586751773467</v>
+        <v>-6.690147155399936</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.404095949938307</v>
       </c>
       <c r="E49">
-        <v>-19.36966206361205</v>
+        <v>-16.85773564545334</v>
       </c>
       <c r="F49">
-        <v>2.228830866114329</v>
+        <v>3.101988094383204</v>
       </c>
       <c r="G49">
-        <v>-7.695401879680776</v>
+        <v>-7.09944345150351</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.542933676498834</v>
       </c>
       <c r="E50">
-        <v>-18.8255885539605</v>
+        <v>-18.0894398192736</v>
       </c>
       <c r="F50">
-        <v>2.882944558795736</v>
+        <v>4.191344244578333</v>
       </c>
       <c r="G50">
-        <v>-7.578042428164117</v>
+        <v>-8.073667663496682</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.685196240290578</v>
       </c>
       <c r="E51">
-        <v>-16.57478753250608</v>
+        <v>-16.72324449589953</v>
       </c>
       <c r="F51">
-        <v>2.629155980865246</v>
+        <v>3.690152144658131</v>
       </c>
       <c r="G51">
-        <v>-8.039267336667463</v>
+        <v>-7.959809275383949</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.823093380932402</v>
       </c>
       <c r="E52">
-        <v>-16.62562871019019</v>
+        <v>-15.48236110526572</v>
       </c>
       <c r="F52">
-        <v>3.255328841050226</v>
+        <v>4.327131885980033</v>
       </c>
       <c r="G52">
-        <v>-7.800666748529322</v>
+        <v>-7.405525642233192</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.950390442568095</v>
       </c>
       <c r="E53">
-        <v>-15.48590237193972</v>
+        <v>-14.91059597705726</v>
       </c>
       <c r="F53">
-        <v>2.650264439023383</v>
+        <v>3.573228085752981</v>
       </c>
       <c r="G53">
-        <v>-8.51898520987984</v>
+        <v>-8.480772103598547</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.062075640260924</v>
       </c>
       <c r="E54">
-        <v>-14.35811761964747</v>
+        <v>-12.62352640727541</v>
       </c>
       <c r="F54">
-        <v>2.626901164794825</v>
+        <v>3.596414089357339</v>
       </c>
       <c r="G54">
-        <v>-9.028056891163009</v>
+        <v>-7.900350259505252</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.154186247188139</v>
       </c>
       <c r="E55">
-        <v>-14.91446329385981</v>
+        <v>-11.38421439712225</v>
       </c>
       <c r="F55">
-        <v>2.73658860606912</v>
+        <v>3.380221794370307</v>
       </c>
       <c r="G55">
-        <v>-7.915053413313124</v>
+        <v>-8.800996359249435</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.224887541732053</v>
       </c>
       <c r="E56">
-        <v>-14.69947851881967</v>
+        <v>-14.35740664922826</v>
       </c>
       <c r="F56">
-        <v>2.771169631666388</v>
+        <v>2.41632685753358</v>
       </c>
       <c r="G56">
-        <v>-8.478704934016097</v>
+        <v>-8.953080978529698</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.272294166675196</v>
       </c>
       <c r="E57">
-        <v>-13.28236503370335</v>
+        <v>-12.43984244457628</v>
       </c>
       <c r="F57">
-        <v>2.628945575544935</v>
+        <v>3.133159559750549</v>
       </c>
       <c r="G57">
-        <v>-9.680540923144829</v>
+        <v>-9.112279286150835</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.294203239412677</v>
       </c>
       <c r="E58">
-        <v>-12.26991598591246</v>
+        <v>-11.27034591819938</v>
       </c>
       <c r="F58">
-        <v>2.3395471397029</v>
+        <v>3.383876551351459</v>
       </c>
       <c r="G58">
-        <v>-8.503038473100938</v>
+        <v>-8.947545557758914</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.291110222122606</v>
       </c>
       <c r="E59">
-        <v>-12.92518617482236</v>
+        <v>-12.34801404864874</v>
       </c>
       <c r="F59">
-        <v>2.477591253909826</v>
+        <v>3.701470956849984</v>
       </c>
       <c r="G59">
-        <v>-9.679572962784793</v>
+        <v>-8.587395398172703</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.264635944184421</v>
       </c>
       <c r="E60">
-        <v>-12.64514081371402</v>
+        <v>-10.54879698371322</v>
       </c>
       <c r="F60">
-        <v>2.08274661789583</v>
+        <v>3.166517915061285</v>
       </c>
       <c r="G60">
-        <v>-9.931987493688196</v>
+        <v>-8.826760510934195</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.218119784496878</v>
       </c>
       <c r="E61">
-        <v>-11.90405604235876</v>
+        <v>-9.927331853270575</v>
       </c>
       <c r="F61">
-        <v>2.366213943133821</v>
+        <v>3.428679630699273</v>
       </c>
       <c r="G61">
-        <v>-9.044692684469394</v>
+        <v>-8.828870336396918</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.156657001775108</v>
       </c>
       <c r="E62">
-        <v>-11.30319094017701</v>
+        <v>-9.93186938422626</v>
       </c>
       <c r="F62">
-        <v>2.289729124098537</v>
+        <v>3.352367112083771</v>
       </c>
       <c r="G62">
-        <v>-9.471458204155452</v>
+        <v>-9.208353453411377</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.084726040141042</v>
       </c>
       <c r="E63">
-        <v>-11.43571673201149</v>
+        <v>-8.901736645435415</v>
       </c>
       <c r="F63">
-        <v>2.397357244009471</v>
+        <v>3.134698666384951</v>
       </c>
       <c r="G63">
-        <v>-9.50113029071751</v>
+        <v>-9.300112814321249</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.005611013570971</v>
       </c>
       <c r="E64">
-        <v>-9.335655024850389</v>
+        <v>-7.101238022355719</v>
       </c>
       <c r="F64">
-        <v>2.123725953312322</v>
+        <v>3.729145055042709</v>
       </c>
       <c r="G64">
-        <v>-8.799660902074741</v>
+        <v>-9.324147762244181</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.924885980893085</v>
       </c>
       <c r="E65">
-        <v>-10.08030370524968</v>
+        <v>-10.07172224700514</v>
       </c>
       <c r="F65">
-        <v>2.138578580844517</v>
+        <v>3.235749549117657</v>
       </c>
       <c r="G65">
-        <v>-9.104417479294407</v>
+        <v>-8.97877294334015</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.847419495154288</v>
       </c>
       <c r="E66">
-        <v>-9.61078699166041</v>
+        <v>-9.507093993832774</v>
       </c>
       <c r="F66">
-        <v>1.750765127345484</v>
+        <v>3.111212793780779</v>
       </c>
       <c r="G66">
-        <v>-9.333486118802361</v>
+        <v>-8.492951998027205</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.779159881900301</v>
       </c>
       <c r="E67">
-        <v>-9.514226340394854</v>
+        <v>-8.927743671661466</v>
       </c>
       <c r="F67">
-        <v>1.656311362608673</v>
+        <v>2.643523185099401</v>
       </c>
       <c r="G67">
-        <v>-8.939903592746967</v>
+        <v>-9.753649820710816</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.72564387308629</v>
       </c>
       <c r="E68">
-        <v>-9.56081075251176</v>
+        <v>-7.797386746132861</v>
       </c>
       <c r="F68">
-        <v>1.847435603252186</v>
+        <v>2.539466985429338</v>
       </c>
       <c r="G68">
-        <v>-8.648409713070578</v>
+        <v>-8.939273598207555</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.690339921315021</v>
       </c>
       <c r="E69">
-        <v>-10.08154903560179</v>
+        <v>-7.761729541796464</v>
       </c>
       <c r="F69">
-        <v>1.712905423567935</v>
+        <v>2.81732460661557</v>
       </c>
       <c r="G69">
-        <v>-9.262946417717419</v>
+        <v>-9.403802696821261</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.673474917697498</v>
       </c>
       <c r="E70">
-        <v>-10.31384163829925</v>
+        <v>-9.152849586108752</v>
       </c>
       <c r="F70">
-        <v>1.555452661113416</v>
+        <v>3.343824987426103</v>
       </c>
       <c r="G70">
-        <v>-8.390239919551908</v>
+        <v>-7.059996605915866</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.67727055058145</v>
       </c>
       <c r="E71">
-        <v>-9.326489393458864</v>
+        <v>-8.674411778724371</v>
       </c>
       <c r="F71">
-        <v>0.8772434174193771</v>
+        <v>2.521179946645136</v>
       </c>
       <c r="G71">
-        <v>-6.870634028498752</v>
+        <v>-7.287408228536301</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.701824013338453</v>
       </c>
       <c r="E72">
-        <v>-9.65747555867949</v>
+        <v>-8.216361161322522</v>
       </c>
       <c r="F72">
-        <v>1.054664804485781</v>
+        <v>2.813426309617996</v>
       </c>
       <c r="G72">
-        <v>-7.518265133794152</v>
+        <v>-9.058208036072747</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.748307222955565</v>
       </c>
       <c r="E73">
-        <v>-10.86886046962734</v>
+        <v>-8.642825672520871</v>
       </c>
       <c r="F73">
-        <v>1.279516852301679</v>
+        <v>2.265550736345626</v>
       </c>
       <c r="G73">
-        <v>-7.00088211830091</v>
+        <v>-8.506437818636524</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.816895829922548</v>
       </c>
       <c r="E74">
-        <v>-9.61360370249318</v>
+        <v>-8.902651397184965</v>
       </c>
       <c r="F74">
-        <v>1.397279219018462</v>
+        <v>2.936640990580006</v>
       </c>
       <c r="G74">
-        <v>-6.695685857392278</v>
+        <v>-8.247861153644482</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.906028552763292</v>
       </c>
       <c r="E75">
-        <v>-9.325257648528778</v>
+        <v>-8.892697811316106</v>
       </c>
       <c r="F75">
-        <v>0.6199574723142675</v>
+        <v>1.591228192505521</v>
       </c>
       <c r="G75">
-        <v>-6.516472098258527</v>
+        <v>-7.475661753066323</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.010915076706811</v>
       </c>
       <c r="E76">
-        <v>-9.376855081372174</v>
+        <v>-8.101496418117964</v>
       </c>
       <c r="F76">
-        <v>0.6165818751478594</v>
+        <v>1.985545986851337</v>
       </c>
       <c r="G76">
-        <v>-6.357080198565381</v>
+        <v>-6.825490982283911</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.131281401124096</v>
       </c>
       <c r="E77">
-        <v>-10.50238012513459</v>
+        <v>-9.944621567031861</v>
       </c>
       <c r="F77">
-        <v>0.05924717450292129</v>
+        <v>2.103283502546036</v>
       </c>
       <c r="G77">
-        <v>-6.071899389169363</v>
+        <v>-5.601775807796802</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.26607458738381</v>
       </c>
       <c r="E78">
-        <v>-10.51168613922036</v>
+        <v>-10.24815159434398</v>
       </c>
       <c r="F78">
-        <v>0.820091036830628</v>
+        <v>2.381437679262471</v>
       </c>
       <c r="G78">
-        <v>-6.504961573027995</v>
+        <v>-6.686701872762518</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.417183305872578</v>
       </c>
       <c r="E79">
-        <v>-10.94693136151958</v>
+        <v>-10.86851630560276</v>
       </c>
       <c r="F79">
-        <v>0.5673155522337616</v>
+        <v>2.33772141794713</v>
       </c>
       <c r="G79">
-        <v>-4.119851465132309</v>
+        <v>-7.127077899477154</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.586252521491991</v>
       </c>
       <c r="E80">
-        <v>-11.26790959918325</v>
+        <v>-10.6892430765871</v>
       </c>
       <c r="F80">
-        <v>0.2907087658257563</v>
+        <v>1.835740712259463</v>
       </c>
       <c r="G80">
-        <v>-4.502274556664031</v>
+        <v>-6.130406850795821</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.773850929581159</v>
       </c>
       <c r="E81">
-        <v>-12.03547235806136</v>
+        <v>-10.93050205781975</v>
       </c>
       <c r="F81">
-        <v>0.1103176816203164</v>
+        <v>2.041566817567861</v>
       </c>
       <c r="G81">
-        <v>-4.18715260053808</v>
+        <v>-5.974788355896036</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.976125915950252</v>
       </c>
       <c r="E82">
-        <v>-12.93070638463771</v>
+        <v>-10.89417011085621</v>
       </c>
       <c r="F82">
-        <v>-0.3131909516327505</v>
+        <v>2.047776259619246</v>
       </c>
       <c r="G82">
-        <v>-4.730253830614251</v>
+        <v>-6.281425073069264</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.194917650433569</v>
       </c>
       <c r="E83">
-        <v>-13.22538324526483</v>
+        <v>-11.6080613957954</v>
       </c>
       <c r="F83">
-        <v>0.1735353683323635</v>
+        <v>1.823197573046273</v>
       </c>
       <c r="G83">
-        <v>-4.264231776190996</v>
+        <v>-6.60325712728428</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.429355936720203</v>
       </c>
       <c r="E84">
-        <v>-14.43718477582139</v>
+        <v>-12.74942251316265</v>
       </c>
       <c r="F84">
-        <v>-0.1231079688145563</v>
+        <v>1.426775725497347</v>
       </c>
       <c r="G84">
-        <v>-3.038515056552625</v>
+        <v>-4.822728497824081</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.680512507915272</v>
       </c>
       <c r="E85">
-        <v>-15.14209156832937</v>
+        <v>-12.93082865343592</v>
       </c>
       <c r="F85">
-        <v>-0.3768750091925736</v>
+        <v>1.897765549911478</v>
       </c>
       <c r="G85">
-        <v>-3.289909127551041</v>
+        <v>-4.293923550082411</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.94799503170138</v>
       </c>
       <c r="E86">
-        <v>-16.30307456357185</v>
+        <v>-15.71243928417343</v>
       </c>
       <c r="F86">
-        <v>-0.5426197293491155</v>
+        <v>0.1513160694870724</v>
       </c>
       <c r="G86">
-        <v>-3.399373959995676</v>
+        <v>-4.968851137530832</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.229839750595977</v>
       </c>
       <c r="E87">
-        <v>-17.68406441152898</v>
+        <v>-17.02984482858886</v>
       </c>
       <c r="F87">
-        <v>-0.6803026753684214</v>
+        <v>1.520815306532758</v>
       </c>
       <c r="G87">
-        <v>-2.638862270612258</v>
+        <v>-4.343994991079537</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.518195889890757</v>
       </c>
       <c r="E88">
-        <v>-18.10300259892658</v>
+        <v>-18.05052211365168</v>
       </c>
       <c r="F88">
-        <v>-0.6356114256199852</v>
+        <v>1.476610308449765</v>
       </c>
       <c r="G88">
-        <v>-2.638123995761383</v>
+        <v>-6.3076846892095</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.813532489779152</v>
       </c>
       <c r="E89">
-        <v>-20.97100292830842</v>
+        <v>-17.85778120293722</v>
       </c>
       <c r="F89">
-        <v>-1.2011651876355</v>
+        <v>0.9919905267899702</v>
       </c>
       <c r="G89">
-        <v>-2.837645235126538</v>
+        <v>-3.407941229487387</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.112653353538464</v>
       </c>
       <c r="E90">
-        <v>-21.04292415249823</v>
+        <v>-22.61403292471939</v>
       </c>
       <c r="F90">
-        <v>-1.671548647110783</v>
+        <v>0.8248541493967252</v>
       </c>
       <c r="G90">
-        <v>-2.912260213388311</v>
+        <v>-4.441004306484521</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.416648821378393</v>
       </c>
       <c r="E91">
-        <v>-22.1720176337787</v>
+        <v>-21.46226537408252</v>
       </c>
       <c r="F91">
-        <v>-1.379864745604424</v>
+        <v>1.01668912927184</v>
       </c>
       <c r="G91">
-        <v>-2.225001795319497</v>
+        <v>-3.757758822382907</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.726048953192391</v>
       </c>
       <c r="E92">
-        <v>-25.40620848531679</v>
+        <v>-22.74580246139458</v>
       </c>
       <c r="F92">
-        <v>-1.351264532655368</v>
+        <v>0.6953720406651345</v>
       </c>
       <c r="G92">
-        <v>-2.558485467292101</v>
+        <v>-3.50955737996183</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.040939474542144</v>
       </c>
       <c r="E93">
-        <v>-26.42113913686389</v>
+        <v>-24.80735855406846</v>
       </c>
       <c r="F93">
-        <v>-1.42849736745538</v>
+        <v>0.3897260065845897</v>
       </c>
       <c r="G93">
-        <v>-2.305778907669906</v>
+        <v>-5.519390896882264</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.354719747807334</v>
       </c>
       <c r="E94">
-        <v>-27.9354880158729</v>
+        <v>-28.76435725586684</v>
       </c>
       <c r="F94">
-        <v>-1.994817369318484</v>
+        <v>-0.02764939441814965</v>
       </c>
       <c r="G94">
-        <v>-2.235242487806524</v>
+        <v>-4.124530487076077</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.67162622563041</v>
       </c>
       <c r="E95">
-        <v>-30.2288453718144</v>
+        <v>-30.18331835837829</v>
       </c>
       <c r="F95">
-        <v>-2.327411023379499</v>
+        <v>0.01022107813563535</v>
       </c>
       <c r="G95">
-        <v>-2.786553334224425</v>
+        <v>-3.789540734407688</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.990264541887807</v>
       </c>
       <c r="E96">
-        <v>-32.7437130338411</v>
+        <v>-31.02210495644903</v>
       </c>
       <c r="F96">
-        <v>-2.18019025508436</v>
+        <v>-0.4456427575033774</v>
       </c>
       <c r="G96">
-        <v>-2.447547366367275</v>
+        <v>-4.476671184835684</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.31094350354437</v>
       </c>
       <c r="E97">
-        <v>-33.83884069582704</v>
+        <v>-33.93667837676276</v>
       </c>
       <c r="F97">
-        <v>-2.167623921583892</v>
+        <v>0.03163520386540537</v>
       </c>
       <c r="G97">
-        <v>-3.154653893649171</v>
+        <v>-5.102213106592903</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.63395376659583</v>
       </c>
       <c r="E98">
-        <v>-36.56054867239109</v>
+        <v>-36.75916754236751</v>
       </c>
       <c r="F98">
-        <v>-2.491032637882666</v>
+        <v>-0.2389617770352895</v>
       </c>
       <c r="G98">
-        <v>-2.919734836100726</v>
+        <v>-5.039164434328173</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.94976981127087</v>
       </c>
       <c r="E99">
-        <v>-38.88657896829793</v>
+        <v>-36.52124831071551</v>
       </c>
       <c r="F99">
-        <v>-2.241245074507698</v>
+        <v>0.5316783581979241</v>
       </c>
       <c r="G99">
-        <v>-2.819637891208306</v>
+        <v>-5.923811297748504</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.25032678082814</v>
       </c>
       <c r="E100">
-        <v>-40.68958636597787</v>
+        <v>-39.41349635417142</v>
       </c>
       <c r="F100">
-        <v>-2.463040446607265</v>
+        <v>0.07656005322143096</v>
       </c>
       <c r="G100">
-        <v>-4.347358243177968</v>
+        <v>-5.565885806379596</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.52065294733688</v>
       </c>
       <c r="E101">
-        <v>-42.89973074779143</v>
+        <v>-42.0988565341129</v>
       </c>
       <c r="F101">
-        <v>-2.437530044070652</v>
+        <v>0.07918680625570819</v>
       </c>
       <c r="G101">
-        <v>-3.677001397361853</v>
+        <v>-5.760242403010184</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.76250005807711</v>
       </c>
       <c r="E102">
-        <v>-43.67978077374568</v>
+        <v>-47.59867689524354</v>
       </c>
       <c r="F102">
-        <v>-2.358760587738447</v>
+        <v>-0.5700991612021835</v>
       </c>
       <c r="G102">
-        <v>-5.024490811514337</v>
+        <v>-5.927922668362488</v>
       </c>
     </row>
   </sheetData>
